--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8C814E-0723-4877-BE74-257A604D3958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE318DCE-8876-44ED-87C5-99F42F61374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4608,7 +4608,7 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" s="24">
-        <f t="shared" ref="A12:A22" si="5">(B12*1000000) + (C12*100000) + D12</f>
+        <f t="shared" ref="A12:A20" si="5">(B12*1000000) + (C12*100000) + D12</f>
         <v>20102005</v>
       </c>
       <c r="B12" s="35">
@@ -4645,7 +4645,7 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" s="24">
-        <f t="shared" ref="A13:A22" si="6">(B13*1000000) + (C13*10000) + D13</f>
+        <f t="shared" ref="A13:A21" si="6">(B13*1000000) + (C13*10000) + D13</f>
         <v>20012006</v>
       </c>
       <c r="B13" s="35">
@@ -4719,7 +4719,7 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="24">
-        <f t="shared" ref="A15:A22" si="8">(B15*1000000) + (C15*10000) + D15</f>
+        <f t="shared" ref="A15:A19" si="8">(B15*1000000) + (C15*10000) + D15</f>
         <v>20012008</v>
       </c>
       <c r="B15" s="35">

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE318DCE-8876-44ED-87C5-99F42F61374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1707F8-270B-4B0B-B3D8-D3BBE8A2B68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -726,7 +726,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="122">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1040,10 +1040,6 @@
     <t>double</t>
   </si>
   <si>
-    <t>Table_Skilll</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬 이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1176,6 +1172,26 @@
   </si>
   <si>
     <t>Buff_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qte 종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTE 판정 횟수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTE 판정 보정치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qte 판정 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table_Skill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3762,7 +3778,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
         <v>72</v>
@@ -3770,7 +3786,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
         <v>73</v>
@@ -3778,12 +3794,12 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
         <v>78</v>
@@ -3791,7 +3807,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
         <v>79</v>
@@ -4162,7 +4178,7 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4175,51 +4191,59 @@
         <v>60</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>76</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G2" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="22" t="s">
-        <v>89</v>
-      </c>
       <c r="I2" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="J2" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="K2" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="L2" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="M2" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="O2" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="M2" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="N2" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>104</v>
-      </c>
       <c r="P2" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
+        <v>115</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="R2" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="S2" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="T2" s="22" t="s">
+        <v>119</v>
+      </c>
       <c r="U2" s="22"/>
       <c r="V2" s="22"/>
       <c r="W2" s="22"/>
@@ -4247,16 +4271,16 @@
         <v>70</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I3" s="29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J3" s="29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K3" s="29" t="s">
         <v>58</v>
@@ -4271,7 +4295,7 @@
         <v>58</v>
       </c>
       <c r="O3" s="29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P3" s="29" t="s">
         <v>58</v>
@@ -4301,40 +4325,40 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>85</v>
-      </c>
       <c r="G4" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="M4" s="26" t="s">
-        <v>111</v>
-      </c>
       <c r="N4" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="O4" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="O4" s="26" t="s">
-        <v>115</v>
-      </c>
       <c r="P4" s="26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q4" s="26"/>
       <c r="R4" s="26"/>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1707F8-270B-4B0B-B3D8-D3BBE8A2B68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C9CE05-C023-4476-ACC2-D6FF5A965A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -1199,9 +1199,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="00"/>
     <numFmt numFmtId="178" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
@@ -1371,7 +1370,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1462,25 +1461,19 @@
     <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4153,10 +4146,10 @@
   <dimension ref="A1:Z22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.375" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.375" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.125" style="34" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.125" customWidth="1"/>
     <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
@@ -4182,6 +4175,7 @@
       </c>
       <c r="B1"/>
       <c r="C1"/>
+      <c r="D1"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
@@ -4253,16 +4247,16 @@
     </row>
     <row r="3" spans="1:26" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>70</v>
@@ -4372,35 +4366,35 @@
       <c r="Z4" s="26"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="24">
+      <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>20001001</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="33">
         <v>20</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>0</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>1001</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="34"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="31"/>
       <c r="H5" s="24"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="33"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="30"/>
       <c r="U5" s="25"/>
       <c r="V5" s="25"/>
       <c r="W5" s="25"/>
@@ -4409,35 +4403,35 @@
       <c r="Z5" s="25"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="24">
+      <c r="A6" s="25">
         <f>(B6*1000000) + (C6*100000) + D6</f>
         <v>20001002</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="33">
         <v>20</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>0</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>1002</v>
       </c>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="34"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="31"/>
       <c r="H6" s="24"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
       <c r="K6" s="24"/>
       <c r="L6" s="24"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
       <c r="S6" s="24"/>
-      <c r="T6" s="33"/>
+      <c r="T6" s="30"/>
       <c r="U6" s="25"/>
       <c r="V6" s="25"/>
       <c r="W6" s="25"/>
@@ -4446,536 +4440,536 @@
       <c r="Z6" s="25"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="25">
         <f t="shared" ref="A7" si="0">(B7*1000000) + (C7*10000) + D7</f>
         <v>20001003</v>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="33">
         <v>20</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>0</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>1003</v>
       </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="34"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="31"/>
       <c r="H7" s="24"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
       <c r="K7" s="24"/>
       <c r="L7" s="24"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
       <c r="S7" s="24"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="33"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="24">
+      <c r="A8" s="25">
         <f t="shared" ref="A8" si="1">(B8*1000000) + (C8*100000) + D8</f>
         <v>20102001</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="33">
         <v>20</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>1</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>2001</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="34"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="24"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
       <c r="K8" s="24"/>
       <c r="L8" s="24"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
       <c r="S8" s="24"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="24">
+      <c r="A9" s="25">
         <f t="shared" ref="A9" si="2">(B9*1000000) + (C9*10000) + D9</f>
         <v>20012002</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="33">
         <v>20</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>1</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>2002</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="31"/>
       <c r="H9" s="24"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
       <c r="K9" s="24"/>
       <c r="L9" s="24"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
       <c r="S9" s="24"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="33"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="24">
+      <c r="A10" s="25">
         <f t="shared" ref="A10" si="3">(B10*1000000) + (C10*100000) + D10</f>
         <v>20102003</v>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="33">
         <v>20</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="25">
         <v>1</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>2003</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="34"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="24"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
       <c r="K10" s="24"/>
       <c r="L10" s="24"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="30"/>
       <c r="S10" s="24"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="33"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
+      <c r="A11" s="25">
         <f t="shared" ref="A11" si="4">(B11*1000000) + (C11*10000) + D11</f>
         <v>20012004</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="33">
         <v>20</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="25">
         <v>1</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>2004</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="34"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="31"/>
       <c r="H11" s="24"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
       <c r="K11" s="24"/>
       <c r="L11" s="24"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
       <c r="S11" s="24"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="33"/>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33"/>
-      <c r="Y11" s="33"/>
-      <c r="Z11" s="33"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A12" s="24">
+      <c r="A12" s="25">
         <f t="shared" ref="A12:A20" si="5">(B12*1000000) + (C12*100000) + D12</f>
         <v>20102005</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="33">
         <v>20</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="25">
         <v>1</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>2005</v>
       </c>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="34"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="24"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
       <c r="K12" s="24"/>
       <c r="L12" s="24"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
       <c r="S12" s="24"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="33"/>
-      <c r="Z12" s="33"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="24">
+      <c r="A13" s="25">
         <f t="shared" ref="A13:A21" si="6">(B13*1000000) + (C13*10000) + D13</f>
         <v>20012006</v>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="33">
         <v>20</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="25">
         <v>1</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>2006</v>
       </c>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="24"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
       <c r="K13" s="24"/>
       <c r="L13" s="24"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="33"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="30"/>
       <c r="S13" s="24"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
-      <c r="Z13" s="33"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="30"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="30"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A14" s="24">
+      <c r="A14" s="25">
         <f t="shared" ref="A14:A22" si="7">(B14*1000000) + (C14*100000) + D14</f>
         <v>20102007</v>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="33">
         <v>20</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="25">
         <v>1</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>2007</v>
       </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="34"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="24"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
       <c r="K14" s="24"/>
       <c r="L14" s="24"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="33"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="30"/>
       <c r="S14" s="24"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="33"/>
-      <c r="Z14" s="33"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
+      <c r="X14" s="30"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="30"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A15" s="24">
+      <c r="A15" s="25">
         <f t="shared" ref="A15:A19" si="8">(B15*1000000) + (C15*10000) + D15</f>
         <v>20012008</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="33">
         <v>20</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="25">
         <v>1</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>2008</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="34"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="31"/>
       <c r="H15" s="24"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
       <c r="K15" s="24"/>
       <c r="L15" s="24"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="33"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="30"/>
       <c r="S15" s="24"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="30"/>
+      <c r="X15" s="30"/>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="30"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A16" s="24">
+      <c r="A16" s="25">
         <f t="shared" si="5"/>
         <v>20102009</v>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="33">
         <v>20</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="25">
         <v>1</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>2009</v>
       </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="34"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="24"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
       <c r="K16" s="24"/>
       <c r="L16" s="24"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="33"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="30"/>
       <c r="S16" s="24"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="33"/>
-      <c r="Z16" s="33"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="24">
+      <c r="A17" s="25">
         <f t="shared" si="6"/>
         <v>20012010</v>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="33">
         <v>20</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="25">
         <v>1</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <v>2010</v>
       </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="24">
+      <c r="A18" s="25">
         <f t="shared" si="7"/>
         <v>20102011</v>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="33">
         <v>20</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="25">
         <v>1</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="25">
         <v>2011</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="24">
+      <c r="A19" s="25">
         <f t="shared" si="8"/>
         <v>20012012</v>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="33">
         <v>20</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="25">
         <v>1</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <v>2012</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="24">
+      <c r="A20" s="25">
         <f t="shared" si="5"/>
         <v>20102013</v>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="33">
         <v>20</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="25">
         <v>1</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="25">
         <v>2013</v>
       </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="24">
+      <c r="A21" s="25">
         <f t="shared" si="6"/>
         <v>20012014</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="33">
         <v>20</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="25">
         <v>1</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <v>2014</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="24">
+      <c r="A22" s="25">
         <f t="shared" si="7"/>
         <v>20102015</v>
       </c>
-      <c r="B22" s="35">
+      <c r="B22" s="33">
         <v>20</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="25">
         <v>1</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="25">
         <v>2015</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C9CE05-C023-4476-ACC2-D6FF5A965A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67165C24-3D03-4A3F-A982-512CB525094C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1082,13 +1082,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>enum:SKILL_SIDE:NONE</t>
-  </si>
-  <si>
-    <t>enum:SKILL_SIDE:NONE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>enum:SKILL_TARGET_TYPE:NONE</t>
   </si>
   <si>
@@ -1192,6 +1185,13 @@
   </si>
   <si>
     <t>Table_Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:SIDE:NONE</t>
+  </si>
+  <si>
+    <t>enum:SIDE:NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1201,7 +1201,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="178" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="177" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1464,7 +1464,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
@@ -3787,12 +3787,12 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
         <v>78</v>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
         <v>79</v>
@@ -4171,7 +4171,7 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4203,40 +4203,40 @@
         <v>88</v>
       </c>
       <c r="I2" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="K2" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="L2" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="M2" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="O2" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="L2" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="M2" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="N2" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>103</v>
-      </c>
       <c r="P2" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="R2" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="Q2" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="R2" s="22" t="s">
+      <c r="S2" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="T2" s="22" t="s">
         <v>117</v>
-      </c>
-      <c r="S2" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="T2" s="22" t="s">
-        <v>119</v>
       </c>
       <c r="U2" s="22"/>
       <c r="V2" s="22"/>
@@ -4271,10 +4271,10 @@
         <v>91</v>
       </c>
       <c r="I3" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="29" t="s">
         <v>93</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>95</v>
       </c>
       <c r="K3" s="29" t="s">
         <v>58</v>
@@ -4289,7 +4289,7 @@
         <v>58</v>
       </c>
       <c r="O3" s="29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P3" s="29" t="s">
         <v>58</v>
@@ -4325,34 +4325,34 @@
         <v>84</v>
       </c>
       <c r="G4" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="I4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="L4" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>110</v>
-      </c>
       <c r="N4" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O4" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="P4" s="26" t="s">
         <v>114</v>
-      </c>
-      <c r="P4" s="26" t="s">
-        <v>116</v>
       </c>
       <c r="Q4" s="26"/>
       <c r="R4" s="26"/>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67165C24-3D03-4A3F-A982-512CB525094C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF519C3-610F-4F1B-A856-A5837C23A336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -345,6 +345,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>전세혁</author>
+    <author>제동우</author>
   </authors>
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{4E6B084F-FA63-4203-8F0E-6D0C0A5F7A83}">
@@ -480,6 +481,127 @@
             <charset val="129"/>
           </rPr>
           <t>캐릭터</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="1" shapeId="0" xr:uid="{6770E550-A25B-4524-BAFB-4B5D51F1AB46}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>필요한</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>경우</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기입
+필요</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>없는</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>경우</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> "-" </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기입</t>
         </r>
       </text>
     </comment>
@@ -726,7 +848,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="120">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1168,22 +1290,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>qte 종류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTE 판정 횟수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTE 판정 보정치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qte 판정 여부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Table_Skill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1192,6 +1298,14 @@
   </si>
   <si>
     <t>enum:SIDE:NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTE ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTE_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3787,7 +3901,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -4171,7 +4285,7 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4229,15 +4343,9 @@
       <c r="Q2" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="R2" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="S2" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="T2" s="22" t="s">
-        <v>117</v>
-      </c>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
       <c r="U2" s="22"/>
       <c r="V2" s="22"/>
       <c r="W2" s="22"/>
@@ -4271,7 +4379,7 @@
         <v>91</v>
       </c>
       <c r="I3" s="29" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>93</v>
@@ -4294,7 +4402,9 @@
       <c r="P3" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="Q3" s="29"/>
+      <c r="Q3" s="29" t="s">
+        <v>58</v>
+      </c>
       <c r="R3" s="29"/>
       <c r="S3" s="29"/>
       <c r="T3" s="29"/>
@@ -4354,7 +4464,9 @@
       <c r="P4" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="Q4" s="26"/>
+      <c r="Q4" s="26" t="s">
+        <v>119</v>
+      </c>
       <c r="R4" s="26"/>
       <c r="S4" s="26"/>
       <c r="T4" s="26"/>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF519C3-610F-4F1B-A856-A5837C23A336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1671AC82-7C70-436F-8C9A-D89BB3C6DF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
     <sheet name="!Desc" sheetId="1" r:id="rId2"/>
-    <sheet name="!Skill_Table" sheetId="3" r:id="rId3"/>
+    <sheet name="SkillTable" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1671AC82-7C70-436F-8C9A-D89BB3C6DF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8FE279-6D49-46B5-8422-2DFB01499B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -848,7 +848,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="121">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1306,6 +1306,10 @@
   </si>
   <si>
     <t>QTE_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4417,7 +4421,7 @@
     </row>
     <row r="4" spans="1:26" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>59</v>
@@ -4836,8 +4840,8 @@
       <c r="N14" s="31"/>
       <c r="O14" s="31"/>
       <c r="P14" s="31"/>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="30"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="32"/>
       <c r="S14" s="24"/>
       <c r="T14" s="30"/>
       <c r="U14" s="30"/>
@@ -4873,8 +4877,8 @@
       <c r="N15" s="31"/>
       <c r="O15" s="31"/>
       <c r="P15" s="31"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="30"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="32"/>
       <c r="S15" s="24"/>
       <c r="T15" s="30"/>
       <c r="U15" s="30"/>
@@ -4910,8 +4914,8 @@
       <c r="N16" s="31"/>
       <c r="O16" s="31"/>
       <c r="P16" s="31"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="30"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="32"/>
       <c r="S16" s="24"/>
       <c r="T16" s="30"/>
       <c r="U16" s="30"/>
@@ -4921,7 +4925,7 @@
       <c r="Y16" s="30"/>
       <c r="Z16" s="30"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
         <f t="shared" si="6"/>
         <v>20012010</v>
@@ -4947,8 +4951,9 @@
       <c r="N17" s="30"/>
       <c r="O17" s="30"/>
       <c r="P17" s="30"/>
+      <c r="Q17" s="30"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="25">
         <f t="shared" si="7"/>
         <v>20102011</v>
@@ -4974,8 +4979,9 @@
       <c r="N18" s="30"/>
       <c r="O18" s="30"/>
       <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="25">
         <f t="shared" si="8"/>
         <v>20012012</v>
@@ -5001,8 +5007,9 @@
       <c r="N19" s="30"/>
       <c r="O19" s="30"/>
       <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="25">
         <f t="shared" si="5"/>
         <v>20102013</v>
@@ -5028,8 +5035,9 @@
       <c r="N20" s="30"/>
       <c r="O20" s="30"/>
       <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
         <f t="shared" si="6"/>
         <v>20012014</v>
@@ -5055,8 +5063,9 @@
       <c r="N21" s="30"/>
       <c r="O21" s="30"/>
       <c r="P21" s="30"/>
+      <c r="Q21" s="30"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="25">
         <f t="shared" si="7"/>
         <v>20102015</v>
@@ -5082,6 +5091,7 @@
       <c r="N22" s="30"/>
       <c r="O22" s="30"/>
       <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8FE279-6D49-46B5-8422-2DFB01499B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EE70E9-B373-49E4-A14A-A6E17083D507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -848,7 +848,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="136">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1310,6 +1310,66 @@
   </si>
   <si>
     <t>Skill_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_NAME_3001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_NAME_3002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_NAME_3003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_DESC_4001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_DESC_4002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_DESC_4003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_ACTIVE_NAME_5001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_ACTIVE_NAME_5002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_ACTIVE_NAME_5003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_ACTIVE_DESC_6001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_ACTIVE_DESC_6002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_ACTIVE_DESC_6003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_ACTIVE_NAME_5004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_ACTIVE_DESC_6004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1317,9 +1377,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="181" formatCode="00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1488,7 +1550,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1592,6 +1654,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4266,16 +4343,16 @@
   <cols>
     <col min="1" max="1" width="15.5" style="34" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.375" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="38" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.125" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.125" customWidth="1"/>
-    <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25" style="39" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="28.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.875" style="36" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30.375" customWidth="1"/>
     <col min="15" max="15" width="30.375" bestFit="1" customWidth="1"/>
@@ -4294,6 +4371,8 @@
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
+      <c r="G1"/>
+      <c r="L1"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
@@ -4404,10 +4483,10 @@
         <v>95</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="Q3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="R3" s="29"/>
       <c r="S3" s="29"/>
@@ -4489,25 +4568,51 @@
       <c r="B5" s="33">
         <v>20</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="37">
         <v>0</v>
       </c>
       <c r="D5" s="25">
         <v>1001</v>
       </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="30"/>
+      <c r="E5" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="24">
+        <v>0</v>
+      </c>
+      <c r="H5" s="24">
+        <v>1</v>
+      </c>
+      <c r="I5" s="31">
+        <v>1</v>
+      </c>
+      <c r="J5" s="31">
+        <v>0</v>
+      </c>
+      <c r="K5" s="24">
+        <v>0</v>
+      </c>
+      <c r="L5" s="35">
+        <v>0</v>
+      </c>
+      <c r="M5" s="31">
+        <v>0</v>
+      </c>
+      <c r="N5" s="31">
+        <v>0</v>
+      </c>
+      <c r="O5" s="31">
+        <v>0</v>
+      </c>
+      <c r="P5" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q5" s="30" t="s">
+        <v>121</v>
+      </c>
       <c r="R5" s="30"/>
       <c r="S5" s="31"/>
       <c r="T5" s="30"/>
@@ -4520,31 +4625,57 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
-        <f>(B6*1000000) + (C6*100000) + D6</f>
+        <f t="shared" ref="A6:A22" si="0">(B6*1000000) + (C6*10000) + D6</f>
         <v>20001002</v>
       </c>
       <c r="B6" s="33">
         <v>20</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="37">
         <v>0</v>
       </c>
       <c r="D6" s="25">
         <v>1002</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="30"/>
+      <c r="E6" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="24">
+        <v>0</v>
+      </c>
+      <c r="H6" s="24">
+        <v>1</v>
+      </c>
+      <c r="I6" s="31">
+        <v>1</v>
+      </c>
+      <c r="J6" s="31">
+        <v>0</v>
+      </c>
+      <c r="K6" s="24">
+        <v>0</v>
+      </c>
+      <c r="L6" s="35">
+        <v>0</v>
+      </c>
+      <c r="M6" s="31">
+        <v>0</v>
+      </c>
+      <c r="N6" s="31">
+        <v>0</v>
+      </c>
+      <c r="O6" s="31">
+        <v>0</v>
+      </c>
+      <c r="P6" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q6" s="30" t="s">
+        <v>121</v>
+      </c>
       <c r="R6" s="30"/>
       <c r="S6" s="24"/>
       <c r="T6" s="30"/>
@@ -4557,31 +4688,57 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
-        <f t="shared" ref="A7" si="0">(B7*1000000) + (C7*10000) + D7</f>
+        <f t="shared" si="0"/>
         <v>20001003</v>
       </c>
       <c r="B7" s="33">
         <v>20</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="37">
         <v>0</v>
       </c>
       <c r="D7" s="25">
         <v>1003</v>
       </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="30"/>
+      <c r="E7" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="24">
+        <v>0</v>
+      </c>
+      <c r="H7" s="24">
+        <v>1</v>
+      </c>
+      <c r="I7" s="31">
+        <v>1</v>
+      </c>
+      <c r="J7" s="31">
+        <v>0</v>
+      </c>
+      <c r="K7" s="24">
+        <v>0</v>
+      </c>
+      <c r="L7" s="35">
+        <v>0</v>
+      </c>
+      <c r="M7" s="31">
+        <v>0</v>
+      </c>
+      <c r="N7" s="31">
+        <v>0</v>
+      </c>
+      <c r="O7" s="31">
+        <v>0</v>
+      </c>
+      <c r="P7" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>121</v>
+      </c>
       <c r="R7" s="30"/>
       <c r="S7" s="24"/>
       <c r="T7" s="30"/>
@@ -4594,31 +4751,57 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
-        <f t="shared" ref="A8" si="1">(B8*1000000) + (C8*100000) + D8</f>
-        <v>20102001</v>
+        <f t="shared" si="0"/>
+        <v>20012001</v>
       </c>
       <c r="B8" s="33">
         <v>20</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="37">
         <v>1</v>
       </c>
       <c r="D8" s="25">
         <v>2001</v>
       </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="30"/>
+      <c r="E8" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" s="24">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24">
+        <v>2</v>
+      </c>
+      <c r="I8" s="31">
+        <v>2</v>
+      </c>
+      <c r="J8" s="31">
+        <v>1</v>
+      </c>
+      <c r="K8" s="24">
+        <v>3</v>
+      </c>
+      <c r="L8" s="35">
+        <v>0.7</v>
+      </c>
+      <c r="M8" s="31">
+        <v>3</v>
+      </c>
+      <c r="N8" s="31">
+        <v>0</v>
+      </c>
+      <c r="O8" s="31">
+        <v>2</v>
+      </c>
+      <c r="P8" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q8" s="30" t="s">
+        <v>121</v>
+      </c>
       <c r="R8" s="30"/>
       <c r="S8" s="24"/>
       <c r="T8" s="30"/>
@@ -4631,31 +4814,57 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
-        <f t="shared" ref="A9" si="2">(B9*1000000) + (C9*10000) + D9</f>
+        <f t="shared" si="0"/>
         <v>20012002</v>
       </c>
       <c r="B9" s="33">
         <v>20</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="37">
         <v>1</v>
       </c>
       <c r="D9" s="25">
         <v>2002</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="30"/>
+      <c r="E9" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="24">
+        <v>0</v>
+      </c>
+      <c r="H9" s="24">
+        <v>2</v>
+      </c>
+      <c r="I9" s="31">
+        <v>2</v>
+      </c>
+      <c r="J9" s="31">
+        <v>2</v>
+      </c>
+      <c r="K9" s="24">
+        <v>3</v>
+      </c>
+      <c r="L9" s="35">
+        <v>0.8</v>
+      </c>
+      <c r="M9" s="31">
+        <v>1</v>
+      </c>
+      <c r="N9" s="31">
+        <v>0</v>
+      </c>
+      <c r="O9" s="31">
+        <v>0</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>121</v>
+      </c>
       <c r="R9" s="30"/>
       <c r="S9" s="24"/>
       <c r="T9" s="30"/>
@@ -4668,31 +4877,57 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
-        <f t="shared" ref="A10" si="3">(B10*1000000) + (C10*100000) + D10</f>
-        <v>20102003</v>
+        <f t="shared" si="0"/>
+        <v>20012003</v>
       </c>
       <c r="B10" s="33">
         <v>20</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="37">
         <v>1</v>
       </c>
       <c r="D10" s="25">
         <v>2003</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="30"/>
+      <c r="E10" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="G10" s="24">
+        <v>0</v>
+      </c>
+      <c r="H10" s="24">
+        <v>3</v>
+      </c>
+      <c r="I10" s="31">
+        <v>1</v>
+      </c>
+      <c r="J10" s="31">
+        <v>1</v>
+      </c>
+      <c r="K10" s="24">
+        <v>3</v>
+      </c>
+      <c r="L10" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="M10" s="31">
+        <v>1</v>
+      </c>
+      <c r="N10" s="31">
+        <v>0</v>
+      </c>
+      <c r="O10" s="31">
+        <v>0</v>
+      </c>
+      <c r="P10" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q10" s="30" t="s">
+        <v>121</v>
+      </c>
       <c r="R10" s="30"/>
       <c r="S10" s="24"/>
       <c r="T10" s="30"/>
@@ -4705,31 +4940,57 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
-        <f t="shared" ref="A11" si="4">(B11*1000000) + (C11*10000) + D11</f>
+        <f t="shared" si="0"/>
         <v>20012004</v>
       </c>
       <c r="B11" s="33">
         <v>20</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="37">
         <v>1</v>
       </c>
       <c r="D11" s="25">
         <v>2004</v>
       </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="30"/>
+      <c r="E11" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G11" s="24">
+        <v>0</v>
+      </c>
+      <c r="H11" s="24">
+        <v>4</v>
+      </c>
+      <c r="I11" s="31">
+        <v>1</v>
+      </c>
+      <c r="J11" s="31">
+        <v>1</v>
+      </c>
+      <c r="K11" s="24">
+        <v>3</v>
+      </c>
+      <c r="L11" s="35">
+        <v>0</v>
+      </c>
+      <c r="M11" s="31">
+        <v>0</v>
+      </c>
+      <c r="N11" s="31">
+        <v>2</v>
+      </c>
+      <c r="O11" s="31">
+        <v>0</v>
+      </c>
+      <c r="P11" s="31">
+        <v>30001043</v>
+      </c>
+      <c r="Q11" s="30" t="s">
+        <v>121</v>
+      </c>
       <c r="R11" s="30"/>
       <c r="S11" s="24"/>
       <c r="T11" s="30"/>
@@ -4742,13 +5003,13 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
-        <f t="shared" ref="A12:A20" si="5">(B12*1000000) + (C12*100000) + D12</f>
-        <v>20102005</v>
+        <f t="shared" si="0"/>
+        <v>20012005</v>
       </c>
       <c r="B12" s="33">
         <v>20</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="37">
         <v>1</v>
       </c>
       <c r="D12" s="25">
@@ -4756,12 +5017,12 @@
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="30"/>
-      <c r="G12" s="31"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="24"/>
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
       <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
+      <c r="L12" s="35"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
       <c r="O12" s="31"/>
@@ -4779,13 +5040,13 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
-        <f t="shared" ref="A13:A21" si="6">(B13*1000000) + (C13*10000) + D13</f>
+        <f t="shared" si="0"/>
         <v>20012006</v>
       </c>
       <c r="B13" s="33">
         <v>20</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="37">
         <v>1</v>
       </c>
       <c r="D13" s="25">
@@ -4793,12 +5054,12 @@
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="30"/>
-      <c r="G13" s="31"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="24"/>
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
+      <c r="L13" s="35"/>
       <c r="M13" s="31"/>
       <c r="N13" s="31"/>
       <c r="O13" s="31"/>
@@ -4816,13 +5077,13 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
-        <f t="shared" ref="A14:A22" si="7">(B14*1000000) + (C14*100000) + D14</f>
-        <v>20102007</v>
+        <f t="shared" si="0"/>
+        <v>20012007</v>
       </c>
       <c r="B14" s="33">
         <v>20</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="37">
         <v>1</v>
       </c>
       <c r="D14" s="25">
@@ -4830,12 +5091,12 @@
       </c>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
-      <c r="G14" s="31"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="24"/>
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
+      <c r="L14" s="35"/>
       <c r="M14" s="31"/>
       <c r="N14" s="31"/>
       <c r="O14" s="31"/>
@@ -4853,13 +5114,13 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
-        <f t="shared" ref="A15:A19" si="8">(B15*1000000) + (C15*10000) + D15</f>
+        <f t="shared" si="0"/>
         <v>20012008</v>
       </c>
       <c r="B15" s="33">
         <v>20</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="37">
         <v>1</v>
       </c>
       <c r="D15" s="25">
@@ -4867,12 +5128,12 @@
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="30"/>
-      <c r="G15" s="31"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="24"/>
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
       <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
+      <c r="L15" s="35"/>
       <c r="M15" s="31"/>
       <c r="N15" s="31"/>
       <c r="O15" s="31"/>
@@ -4890,13 +5151,13 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
-        <f t="shared" si="5"/>
-        <v>20102009</v>
+        <f t="shared" si="0"/>
+        <v>20012009</v>
       </c>
       <c r="B16" s="33">
         <v>20</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="37">
         <v>1</v>
       </c>
       <c r="D16" s="25">
@@ -4904,12 +5165,12 @@
       </c>
       <c r="E16" s="30"/>
       <c r="F16" s="30"/>
-      <c r="G16" s="31"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
       <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
+      <c r="L16" s="35"/>
       <c r="M16" s="31"/>
       <c r="N16" s="31"/>
       <c r="O16" s="31"/>
@@ -4927,13 +5188,13 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>20012010</v>
       </c>
       <c r="B17" s="33">
         <v>20</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="37">
         <v>1</v>
       </c>
       <c r="D17" s="25">
@@ -4941,12 +5202,12 @@
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="30"/>
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
       <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
+      <c r="L17" s="35"/>
       <c r="M17" s="30"/>
       <c r="N17" s="30"/>
       <c r="O17" s="30"/>
@@ -4955,13 +5216,13 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="25">
-        <f t="shared" si="7"/>
-        <v>20102011</v>
+        <f t="shared" si="0"/>
+        <v>20012011</v>
       </c>
       <c r="B18" s="33">
         <v>20</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="37">
         <v>1</v>
       </c>
       <c r="D18" s="25">
@@ -4969,12 +5230,12 @@
       </c>
       <c r="E18" s="30"/>
       <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
       <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
+      <c r="L18" s="35"/>
       <c r="M18" s="30"/>
       <c r="N18" s="30"/>
       <c r="O18" s="30"/>
@@ -4983,13 +5244,13 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>20012012</v>
       </c>
       <c r="B19" s="33">
         <v>20</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="37">
         <v>1</v>
       </c>
       <c r="D19" s="25">
@@ -4997,12 +5258,12 @@
       </c>
       <c r="E19" s="30"/>
       <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="30"/>
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
       <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
+      <c r="L19" s="35"/>
       <c r="M19" s="30"/>
       <c r="N19" s="30"/>
       <c r="O19" s="30"/>
@@ -5011,13 +5272,13 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="25">
-        <f t="shared" si="5"/>
-        <v>20102013</v>
+        <f t="shared" si="0"/>
+        <v>20012013</v>
       </c>
       <c r="B20" s="33">
         <v>20</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="37">
         <v>1</v>
       </c>
       <c r="D20" s="25">
@@ -5025,12 +5286,12 @@
       </c>
       <c r="E20" s="30"/>
       <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
+      <c r="G20" s="24"/>
       <c r="H20" s="30"/>
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
       <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
+      <c r="L20" s="35"/>
       <c r="M20" s="30"/>
       <c r="N20" s="30"/>
       <c r="O20" s="30"/>
@@ -5039,13 +5300,13 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>20012014</v>
       </c>
       <c r="B21" s="33">
         <v>20</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="37">
         <v>1</v>
       </c>
       <c r="D21" s="25">
@@ -5053,12 +5314,12 @@
       </c>
       <c r="E21" s="30"/>
       <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="30"/>
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
       <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
+      <c r="L21" s="35"/>
       <c r="M21" s="30"/>
       <c r="N21" s="30"/>
       <c r="O21" s="30"/>
@@ -5067,13 +5328,13 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="25">
-        <f t="shared" si="7"/>
-        <v>20102015</v>
+        <f t="shared" si="0"/>
+        <v>20012015</v>
       </c>
       <c r="B22" s="33">
         <v>20</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="37">
         <v>1</v>
       </c>
       <c r="D22" s="25">
@@ -5081,12 +5342,12 @@
       </c>
       <c r="E22" s="30"/>
       <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="30"/>
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
       <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
+      <c r="L22" s="35"/>
       <c r="M22" s="30"/>
       <c r="N22" s="30"/>
       <c r="O22" s="30"/>
@@ -5099,7 +5360,7 @@
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D44D287-4A0D-4E30-B02E-F978C229F037}">
           <x14:formula1>
             <xm:f>'!Logic'!$A$5:$A$19</xm:f>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EE70E9-B373-49E4-A14A-A6E17083D507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C72FCA-4370-4CFD-9785-643B9FD1AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -848,7 +848,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="137">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1370,6 +1370,10 @@
   </si>
   <si>
     <t>SKILL_ACTIVE_DESC_6004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에셋 파일 경로</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1381,7 +1385,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.0_);[Red]\(0.0\)"/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="181" formatCode="00"/>
+    <numFmt numFmtId="179" formatCode="00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1662,10 +1666,10 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -4426,7 +4430,9 @@
       <c r="Q2" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="R2" s="22"/>
+      <c r="R2" s="22" t="s">
+        <v>136</v>
+      </c>
       <c r="S2" s="22"/>
       <c r="T2" s="22"/>
       <c r="U2" s="22"/>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C72FCA-4370-4CFD-9785-643B9FD1AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AC6CC5-2AC0-4A81-A52C-7B757CF5FDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -484,7 +484,230 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q2" authorId="1" shapeId="0" xr:uid="{6770E550-A25B-4524-BAFB-4B5D51F1AB46}">
+    <comment ref="P2" authorId="1" shapeId="0" xr:uid="{A7CFF224-29C3-46F4-8C48-555C52934D08}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>개의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>스킬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>안에</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>버프가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>개</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이상</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>있는</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>경우를</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>위해</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>배열로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>선언</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="1" shapeId="0" xr:uid="{6770E550-A25B-4524-BAFB-4B5D51F1AB46}">
       <text>
         <r>
           <rPr>
@@ -848,7 +1071,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="140">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1374,6 +1597,17 @@
   </si>
   <si>
     <t>에셋 파일 경로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>버프 수치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1554,7 +1788,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1673,6 +1907,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4342,7 +4579,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5" style="34" bestFit="1" customWidth="1"/>
@@ -4360,15 +4597,16 @@
     <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30.375" customWidth="1"/>
     <col min="15" max="15" width="30.375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.125" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.125" customWidth="1"/>
+    <col min="18" max="18" width="28" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>115</v>
       </c>
@@ -4377,8 +4615,9 @@
       <c r="D1"/>
       <c r="G1"/>
       <c r="L1"/>
+      <c r="P1"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>77</v>
       </c>
@@ -4428,12 +4667,14 @@
         <v>113</v>
       </c>
       <c r="Q2" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="R2" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="R2" s="22" t="s">
+      <c r="S2" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="S2" s="22"/>
       <c r="T2" s="22"/>
       <c r="U2" s="22"/>
       <c r="V2" s="22"/>
@@ -4441,8 +4682,9 @@
       <c r="X2" s="22"/>
       <c r="Y2" s="22"/>
       <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
     </row>
-    <row r="3" spans="1:26" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>70</v>
       </c>
@@ -4489,12 +4731,14 @@
         <v>95</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q3" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="R3" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="Q3" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="R3" s="29"/>
       <c r="S3" s="29"/>
       <c r="T3" s="29"/>
       <c r="U3" s="29"/>
@@ -4503,8 +4747,9 @@
       <c r="X3" s="29"/>
       <c r="Y3" s="29"/>
       <c r="Z3" s="29"/>
+      <c r="AA3" s="29"/>
     </row>
-    <row r="4" spans="1:26" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>120</v>
       </c>
@@ -4554,9 +4799,11 @@
         <v>114</v>
       </c>
       <c r="Q4" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="R4" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="R4" s="26"/>
       <c r="S4" s="26"/>
       <c r="T4" s="26"/>
       <c r="U4" s="26"/>
@@ -4565,8 +4812,9 @@
       <c r="X4" s="26"/>
       <c r="Y4" s="26"/>
       <c r="Z4" s="26"/>
+      <c r="AA4" s="26"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>20001001</v>
@@ -4613,23 +4861,26 @@
       <c r="O5" s="31">
         <v>0</v>
       </c>
-      <c r="P5" s="31" t="s">
+      <c r="P5" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="Q5" s="30" t="s">
+      <c r="Q5" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="R5" s="30"/>
-      <c r="S5" s="31"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="25"/>
+      <c r="R5" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S5" s="30"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="30"/>
       <c r="V5" s="25"/>
       <c r="W5" s="25"/>
       <c r="X5" s="25"/>
       <c r="Y5" s="25"/>
       <c r="Z5" s="25"/>
+      <c r="AA5" s="25"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <f t="shared" ref="A6:A22" si="0">(B6*1000000) + (C6*10000) + D6</f>
         <v>20001002</v>
@@ -4676,23 +4927,26 @@
       <c r="O6" s="31">
         <v>0</v>
       </c>
-      <c r="P6" s="31" t="s">
+      <c r="P6" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="Q6" s="30" t="s">
+      <c r="Q6" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="R6" s="30"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="25"/>
+      <c r="R6" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S6" s="30"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="30"/>
       <c r="V6" s="25"/>
       <c r="W6" s="25"/>
       <c r="X6" s="25"/>
       <c r="Y6" s="25"/>
       <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <f t="shared" si="0"/>
         <v>20001003</v>
@@ -4739,23 +4993,26 @@
       <c r="O7" s="31">
         <v>0</v>
       </c>
-      <c r="P7" s="31" t="s">
+      <c r="P7" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="Q7" s="30" t="s">
+      <c r="Q7" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="R7" s="30"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="30"/>
+      <c r="R7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S7" s="30"/>
+      <c r="T7" s="24"/>
       <c r="U7" s="30"/>
       <c r="V7" s="30"/>
       <c r="W7" s="30"/>
       <c r="X7" s="30"/>
       <c r="Y7" s="30"/>
       <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <f t="shared" si="0"/>
         <v>20012001</v>
@@ -4802,23 +5059,26 @@
       <c r="O8" s="31">
         <v>2</v>
       </c>
-      <c r="P8" s="31" t="s">
+      <c r="P8" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="Q8" s="30" t="s">
+      <c r="Q8" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="R8" s="30"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="30"/>
+      <c r="R8" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S8" s="30"/>
+      <c r="T8" s="24"/>
       <c r="U8" s="30"/>
       <c r="V8" s="30"/>
       <c r="W8" s="30"/>
       <c r="X8" s="30"/>
       <c r="Y8" s="30"/>
       <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <f t="shared" si="0"/>
         <v>20012002</v>
@@ -4865,23 +5125,26 @@
       <c r="O9" s="31">
         <v>0</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="P9" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="Q9" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="R9" s="30"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="30"/>
+      <c r="R9" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S9" s="30"/>
+      <c r="T9" s="24"/>
       <c r="U9" s="30"/>
       <c r="V9" s="30"/>
       <c r="W9" s="30"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <f t="shared" si="0"/>
         <v>20012003</v>
@@ -4928,23 +5191,26 @@
       <c r="O10" s="31">
         <v>0</v>
       </c>
-      <c r="P10" s="31" t="s">
+      <c r="P10" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="Q10" s="30" t="s">
+      <c r="Q10" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="R10" s="30"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="30"/>
+      <c r="R10" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S10" s="30"/>
+      <c r="T10" s="24"/>
       <c r="U10" s="30"/>
       <c r="V10" s="30"/>
       <c r="W10" s="30"/>
       <c r="X10" s="30"/>
       <c r="Y10" s="30"/>
       <c r="Z10" s="30"/>
+      <c r="AA10" s="30"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <f t="shared" si="0"/>
         <v>20012004</v>
@@ -4991,23 +5257,26 @@
       <c r="O11" s="31">
         <v>0</v>
       </c>
-      <c r="P11" s="31">
-        <v>30001043</v>
-      </c>
-      <c r="Q11" s="30" t="s">
+      <c r="P11" s="24">
+        <v>30001025</v>
+      </c>
+      <c r="Q11" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="R11" s="30"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="30"/>
+      <c r="R11" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S11" s="30"/>
+      <c r="T11" s="24"/>
       <c r="U11" s="30"/>
       <c r="V11" s="30"/>
       <c r="W11" s="30"/>
       <c r="X11" s="30"/>
       <c r="Y11" s="30"/>
       <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <f t="shared" si="0"/>
         <v>20012005</v>
@@ -5032,19 +5301,20 @@
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
       <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="30"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="31"/>
       <c r="R12" s="30"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="24"/>
       <c r="U12" s="30"/>
       <c r="V12" s="30"/>
       <c r="W12" s="30"/>
       <c r="X12" s="30"/>
       <c r="Y12" s="30"/>
       <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <f t="shared" si="0"/>
         <v>20012006</v>
@@ -5069,19 +5339,20 @@
       <c r="M13" s="31"/>
       <c r="N13" s="31"/>
       <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="30"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="24"/>
       <c r="U13" s="30"/>
       <c r="V13" s="30"/>
       <c r="W13" s="30"/>
       <c r="X13" s="30"/>
       <c r="Y13" s="30"/>
       <c r="Z13" s="30"/>
+      <c r="AA13" s="30"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
         <f t="shared" si="0"/>
         <v>20012007</v>
@@ -5106,19 +5377,20 @@
       <c r="M14" s="31"/>
       <c r="N14" s="31"/>
       <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="30"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="24"/>
       <c r="U14" s="30"/>
       <c r="V14" s="30"/>
       <c r="W14" s="30"/>
       <c r="X14" s="30"/>
       <c r="Y14" s="30"/>
       <c r="Z14" s="30"/>
+      <c r="AA14" s="30"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
         <f t="shared" si="0"/>
         <v>20012008</v>
@@ -5143,19 +5415,20 @@
       <c r="M15" s="31"/>
       <c r="N15" s="31"/>
       <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="30"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="24"/>
       <c r="U15" s="30"/>
       <c r="V15" s="30"/>
       <c r="W15" s="30"/>
       <c r="X15" s="30"/>
       <c r="Y15" s="30"/>
       <c r="Z15" s="30"/>
+      <c r="AA15" s="30"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
         <f t="shared" si="0"/>
         <v>20012009</v>
@@ -5180,19 +5453,20 @@
       <c r="M16" s="31"/>
       <c r="N16" s="31"/>
       <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="30"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="24"/>
       <c r="U16" s="30"/>
       <c r="V16" s="30"/>
       <c r="W16" s="30"/>
       <c r="X16" s="30"/>
       <c r="Y16" s="30"/>
       <c r="Z16" s="30"/>
+      <c r="AA16" s="30"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
         <f t="shared" si="0"/>
         <v>20012010</v>
@@ -5217,10 +5491,11 @@
       <c r="M17" s="30"/>
       <c r="N17" s="30"/>
       <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
+      <c r="P17" s="24"/>
       <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="25">
         <f t="shared" si="0"/>
         <v>20012011</v>
@@ -5245,10 +5520,11 @@
       <c r="M18" s="30"/>
       <c r="N18" s="30"/>
       <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
+      <c r="P18" s="24"/>
       <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="25">
         <f t="shared" si="0"/>
         <v>20012012</v>
@@ -5273,10 +5549,11 @@
       <c r="M19" s="30"/>
       <c r="N19" s="30"/>
       <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
+      <c r="P19" s="24"/>
       <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="25">
         <f t="shared" si="0"/>
         <v>20012013</v>
@@ -5301,10 +5578,11 @@
       <c r="M20" s="30"/>
       <c r="N20" s="30"/>
       <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
+      <c r="P20" s="24"/>
       <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
         <f t="shared" si="0"/>
         <v>20012014</v>
@@ -5329,10 +5607,11 @@
       <c r="M21" s="30"/>
       <c r="N21" s="30"/>
       <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
+      <c r="P21" s="24"/>
       <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="25">
         <f t="shared" si="0"/>
         <v>20012015</v>
@@ -5357,8 +5636,9 @@
       <c r="M22" s="30"/>
       <c r="N22" s="30"/>
       <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
+      <c r="P22" s="24"/>
       <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5366,7 +5646,7 @@
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D44D287-4A0D-4E30-B02E-F978C229F037}">
           <x14:formula1>
             <xm:f>'!Logic'!$A$5:$A$19</xm:f>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AC6CC5-2AC0-4A81-A52C-7B757CF5FDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7AC014-08BD-4212-AE5C-F77CCBB41B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7AC014-08BD-4212-AE5C-F77CCBB41B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4989CB-5BC9-4E4F-9DE0-9FE774B6184D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1413,13 +1413,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>enum:SKILL_ELEMENT:NONE</t>
-  </si>
-  <si>
-    <t>enum:SKILL_ELEMENT:NONE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>enum:SKILL_TYPE:NONE</t>
   </si>
   <si>
@@ -1427,13 +1420,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>enum:SKILL_TARGET_TYPE:NONE</t>
-  </si>
-  <si>
-    <t>enum:SKILL_TARGET_TYPE:NONE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>enum:SKILL_ELEMENT_RATE:NONE</t>
   </si>
   <si>
@@ -1461,10 +1447,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_Element</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill_Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1608,6 +1590,24 @@
   </si>
   <si>
     <t>Buff_Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:ELEMENT_TYPE:NONE</t>
+  </si>
+  <si>
+    <t>enum:ELEMENT_TYPE:NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:TARGET_TYPE:NONE</t>
+  </si>
+  <si>
+    <t>enum:TARGET_TYPE:NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4207,7 +4207,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="C13" t="s">
         <v>72</v>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
         <v>73</v>
@@ -4223,12 +4223,12 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
         <v>78</v>
@@ -4236,7 +4236,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
         <v>79</v>
@@ -4608,7 +4608,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4643,37 +4643,37 @@
         <v>88</v>
       </c>
       <c r="I2" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="O2" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="M2" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="N2" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>101</v>
-      </c>
       <c r="P2" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="R2" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="R2" s="22" t="s">
-        <v>118</v>
-      </c>
       <c r="S2" s="22" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="T2" s="22"/>
       <c r="U2" s="22"/>
@@ -4704,16 +4704,16 @@
         <v>70</v>
       </c>
       <c r="G3" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="I3" s="29" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J3" s="29" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="K3" s="29" t="s">
         <v>58</v>
@@ -4728,13 +4728,13 @@
         <v>58</v>
       </c>
       <c r="O3" s="29" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="Q3" s="29" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="R3" s="29" t="s">
         <v>70</v>
@@ -4751,7 +4751,7 @@
     </row>
     <row r="4" spans="1:27" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>59</v>
@@ -4769,40 +4769,40 @@
         <v>84</v>
       </c>
       <c r="G4" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="L4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="I4" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="K4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="M4" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="N4" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="O4" s="26" t="s">
-        <v>112</v>
-      </c>
       <c r="P4" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q4" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="R4" s="26" t="s">
         <v>114</v>
-      </c>
-      <c r="Q4" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="R4" s="26" t="s">
-        <v>119</v>
       </c>
       <c r="S4" s="26"/>
       <c r="T4" s="26"/>
@@ -4829,10 +4829,10 @@
         <v>1001</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G5" s="24">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0</v>
       </c>
       <c r="P5" s="24" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="Q5" s="31" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="R5" s="30" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="S5" s="30"/>
       <c r="T5" s="31"/>
@@ -4895,10 +4895,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G6" s="24">
         <v>0</v>
@@ -4928,13 +4928,13 @@
         <v>0</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="Q6" s="31" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="R6" s="30" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="S6" s="30"/>
       <c r="T6" s="24"/>
@@ -4961,10 +4961,10 @@
         <v>1003</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G7" s="24">
         <v>0</v>
@@ -4994,13 +4994,13 @@
         <v>0</v>
       </c>
       <c r="P7" s="24" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="Q7" s="31" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="R7" s="30" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="S7" s="30"/>
       <c r="T7" s="24"/>
@@ -5027,10 +5027,10 @@
         <v>2001</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G8" s="24">
         <v>1</v>
@@ -5060,13 +5060,13 @@
         <v>2</v>
       </c>
       <c r="P8" s="24" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="Q8" s="31" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="R8" s="30" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="S8" s="30"/>
       <c r="T8" s="24"/>
@@ -5093,10 +5093,10 @@
         <v>2002</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G9" s="24">
         <v>0</v>
@@ -5126,13 +5126,13 @@
         <v>0</v>
       </c>
       <c r="P9" s="24" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="Q9" s="31" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="S9" s="30"/>
       <c r="T9" s="24"/>
@@ -5159,10 +5159,10 @@
         <v>2003</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G10" s="24">
         <v>0</v>
@@ -5192,13 +5192,13 @@
         <v>0</v>
       </c>
       <c r="P10" s="24" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="Q10" s="31" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="R10" s="30" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="S10" s="30"/>
       <c r="T10" s="24"/>
@@ -5225,10 +5225,10 @@
         <v>2004</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G11" s="24">
         <v>0</v>
@@ -5261,10 +5261,10 @@
         <v>30001025</v>
       </c>
       <c r="Q11" s="31" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="R11" s="30" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="S11" s="30"/>
       <c r="T11" s="24"/>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4989CB-5BC9-4E4F-9DE0-9FE774B6184D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328FE5FE-C073-419C-9B5E-C140FED1F209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1071,7 +1071,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="141">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1609,6 +1609,9 @@
   <si>
     <t>enum:TARGET_TYPE:NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>double[]</t>
   </si>
 </sst>
 </file>
@@ -4734,7 +4737,7 @@
         <v>132</v>
       </c>
       <c r="Q3" s="29" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="R3" s="29" t="s">
         <v>70</v>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328FE5FE-C073-419C-9B5E-C140FED1F209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F24DEAA-1341-47F4-ACF4-C04008BB5178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
   <si>
     <t>방어력 공식</t>
   </si>
@@ -496,9 +496,6 @@
   </si>
   <si>
     <t>SKILL_PASSIVE_DESC_4001</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>SKILL_PASSIVE_NAME_3002</t>
@@ -9466,12 +9463,8 @@
       <c r="O5" s="32">
         <v>0.0</v>
       </c>
-      <c r="P5" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q5" s="34" t="s">
-        <v>113</v>
-      </c>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="34"/>
       <c r="R5" s="34"/>
       <c r="S5" s="32"/>
       <c r="T5" s="34"/>
@@ -9497,10 +9490,10 @@
         <v>1002.0</v>
       </c>
       <c r="E6" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>114</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>115</v>
       </c>
       <c r="G6" s="31">
         <v>0.0</v>
@@ -9529,12 +9522,8 @@
       <c r="O6" s="32">
         <v>0.0</v>
       </c>
-      <c r="P6" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q6" s="34" t="s">
-        <v>113</v>
-      </c>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="34"/>
       <c r="R6" s="34"/>
       <c r="S6" s="31"/>
       <c r="T6" s="34"/>
@@ -9560,10 +9549,10 @@
         <v>1003.0</v>
       </c>
       <c r="E7" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="31" t="s">
         <v>116</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>117</v>
       </c>
       <c r="G7" s="31">
         <v>0.0</v>
@@ -9592,12 +9581,8 @@
       <c r="O7" s="32">
         <v>0.0</v>
       </c>
-      <c r="P7" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q7" s="34" t="s">
-        <v>113</v>
-      </c>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="34"/>
       <c r="R7" s="34"/>
       <c r="S7" s="31"/>
       <c r="T7" s="34"/>
@@ -9620,13 +9605,13 @@
         <v>1.0</v>
       </c>
       <c r="D8" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="F8" s="31" t="s">
         <v>119</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>120</v>
       </c>
       <c r="G8" s="31">
         <v>1.0</v>
@@ -9655,12 +9640,8 @@
       <c r="O8" s="32">
         <v>2.0</v>
       </c>
-      <c r="P8" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q8" s="34" t="s">
-        <v>113</v>
-      </c>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="34"/>
       <c r="R8" s="34"/>
       <c r="S8" s="31"/>
       <c r="T8" s="34"/>
@@ -9683,13 +9664,13 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="F9" s="31" t="s">
         <v>122</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>123</v>
       </c>
       <c r="G9" s="31">
         <v>0.0</v>
@@ -9718,12 +9699,8 @@
       <c r="O9" s="32">
         <v>0.0</v>
       </c>
-      <c r="P9" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q9" s="34" t="s">
-        <v>113</v>
-      </c>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="34"/>
       <c r="R9" s="34"/>
       <c r="S9" s="31"/>
       <c r="T9" s="34"/>
@@ -9746,13 +9723,13 @@
         <v>1.0</v>
       </c>
       <c r="D10" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="F10" s="31" t="s">
         <v>125</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>126</v>
       </c>
       <c r="G10" s="31">
         <v>0.0</v>
@@ -9781,12 +9758,8 @@
       <c r="O10" s="32">
         <v>0.0</v>
       </c>
-      <c r="P10" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q10" s="34" t="s">
-        <v>113</v>
-      </c>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="34"/>
       <c r="R10" s="34"/>
       <c r="S10" s="31"/>
       <c r="T10" s="34"/>
@@ -9809,13 +9782,13 @@
         <v>1.0</v>
       </c>
       <c r="D11" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="F11" s="31" t="s">
         <v>128</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>129</v>
       </c>
       <c r="G11" s="31">
         <v>0.0</v>
@@ -9847,9 +9820,7 @@
       <c r="P11" s="31">
         <v>3.0001025E7</v>
       </c>
-      <c r="Q11" s="34" t="s">
-        <v>113</v>
-      </c>
+      <c r="Q11" s="34"/>
       <c r="R11" s="34"/>
       <c r="S11" s="31"/>
       <c r="T11" s="34"/>
@@ -9872,13 +9843,13 @@
         <v>1.0</v>
       </c>
       <c r="D12" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="F12" s="36" t="s">
         <v>131</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>132</v>
       </c>
       <c r="G12" s="31"/>
       <c r="H12" s="31"/>
@@ -9913,13 +9884,13 @@
         <v>1.0</v>
       </c>
       <c r="D13" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="36" t="s">
+      <c r="F13" s="36" t="s">
         <v>134</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>135</v>
       </c>
       <c r="G13" s="31"/>
       <c r="H13" s="31"/>
@@ -9954,13 +9925,13 @@
         <v>1.0</v>
       </c>
       <c r="D14" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="E14" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="F14" s="36" t="s">
         <v>137</v>
-      </c>
-      <c r="F14" s="36" t="s">
-        <v>138</v>
       </c>
       <c r="G14" s="31"/>
       <c r="H14" s="31"/>
@@ -9995,13 +9966,13 @@
         <v>1.0</v>
       </c>
       <c r="D15" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="E15" s="36" t="s">
+      <c r="F15" s="36" t="s">
         <v>140</v>
-      </c>
-      <c r="F15" s="36" t="s">
-        <v>141</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31"/>
@@ -10036,13 +10007,13 @@
         <v>1.0</v>
       </c>
       <c r="D16" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="F16" s="36" t="s">
         <v>143</v>
-      </c>
-      <c r="F16" s="36" t="s">
-        <v>144</v>
       </c>
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
@@ -10077,13 +10048,13 @@
         <v>1.0</v>
       </c>
       <c r="D17" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="F17" s="36" t="s">
         <v>146</v>
-      </c>
-      <c r="F17" s="36" t="s">
-        <v>147</v>
       </c>
       <c r="G17" s="31"/>
       <c r="H17" s="34"/>
@@ -10109,13 +10080,13 @@
         <v>1.0</v>
       </c>
       <c r="D18" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="F18" s="36" t="s">
         <v>149</v>
-      </c>
-      <c r="F18" s="36" t="s">
-        <v>150</v>
       </c>
       <c r="G18" s="31"/>
       <c r="H18" s="34"/>
@@ -10141,13 +10112,13 @@
         <v>1.0</v>
       </c>
       <c r="D19" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="F19" s="36" t="s">
         <v>152</v>
-      </c>
-      <c r="F19" s="36" t="s">
-        <v>153</v>
       </c>
       <c r="G19" s="31"/>
       <c r="H19" s="34"/>

--- a/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table_fix.xlsx
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="154">
   <si>
     <t>방어력 공식</t>
   </si>
@@ -496,6 +496,9 @@
   </si>
   <si>
     <t>SKILL_PASSIVE_DESC_4001</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>SKILL_PASSIVE_NAME_3002</t>
@@ -9463,8 +9466,12 @@
       <c r="O5" s="32">
         <v>0.0</v>
       </c>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="34"/>
+      <c r="P5" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q5" s="34" t="s">
+        <v>113</v>
+      </c>
       <c r="R5" s="34"/>
       <c r="S5" s="32"/>
       <c r="T5" s="34"/>
@@ -9490,10 +9497,10 @@
         <v>1002.0</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G6" s="31">
         <v>0.0</v>
@@ -9522,8 +9529,12 @@
       <c r="O6" s="32">
         <v>0.0</v>
       </c>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="34"/>
+      <c r="P6" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q6" s="34" t="s">
+        <v>113</v>
+      </c>
       <c r="R6" s="34"/>
       <c r="S6" s="31"/>
       <c r="T6" s="34"/>
@@ -9549,10 +9560,10 @@
         <v>1003.0</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7" s="31">
         <v>0.0</v>
@@ -9581,8 +9592,12 @@
       <c r="O7" s="32">
         <v>0.0</v>
       </c>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="34"/>
+      <c r="P7" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q7" s="34" t="s">
+        <v>113</v>
+      </c>
       <c r="R7" s="34"/>
       <c r="S7" s="31"/>
       <c r="T7" s="34"/>
@@ -9605,13 +9620,13 @@
         <v>1.0</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G8" s="31">
         <v>1.0</v>
@@ -9640,8 +9655,12 @@
       <c r="O8" s="32">
         <v>2.0</v>
       </c>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="34"/>
+      <c r="P8" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q8" s="34" t="s">
+        <v>113</v>
+      </c>
       <c r="R8" s="34"/>
       <c r="S8" s="31"/>
       <c r="T8" s="34"/>
@@ -9664,13 +9683,13 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G9" s="31">
         <v>0.0</v>
@@ -9699,8 +9718,12 @@
       <c r="O9" s="32">
         <v>0.0</v>
       </c>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="34"/>
+      <c r="P9" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q9" s="34" t="s">
+        <v>113</v>
+      </c>
       <c r="R9" s="34"/>
       <c r="S9" s="31"/>
       <c r="T9" s="34"/>
@@ -9723,13 +9746,13 @@
         <v>1.0</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G10" s="31">
         <v>0.0</v>
@@ -9758,8 +9781,12 @@
       <c r="O10" s="32">
         <v>0.0</v>
       </c>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="34"/>
+      <c r="P10" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q10" s="34" t="s">
+        <v>113</v>
+      </c>
       <c r="R10" s="34"/>
       <c r="S10" s="31"/>
       <c r="T10" s="34"/>
@@ -9782,13 +9809,13 @@
         <v>1.0</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G11" s="31">
         <v>0.0</v>
@@ -9820,7 +9847,9 @@
       <c r="P11" s="31">
         <v>3.0001025E7</v>
       </c>
-      <c r="Q11" s="34"/>
+      <c r="Q11" s="34" t="s">
+        <v>113</v>
+      </c>
       <c r="R11" s="34"/>
       <c r="S11" s="31"/>
       <c r="T11" s="34"/>
@@ -9843,13 +9872,13 @@
         <v>1.0</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G12" s="31"/>
       <c r="H12" s="31"/>
@@ -9884,13 +9913,13 @@
         <v>1.0</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G13" s="31"/>
       <c r="H13" s="31"/>
@@ -9925,13 +9954,13 @@
         <v>1.0</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G14" s="31"/>
       <c r="H14" s="31"/>
@@ -9966,13 +9995,13 @@
         <v>1.0</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31"/>
@@ -10007,13 +10036,13 @@
         <v>1.0</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
@@ -10048,13 +10077,13 @@
         <v>1.0</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G17" s="31"/>
       <c r="H17" s="34"/>
@@ -10080,13 +10109,13 @@
         <v>1.0</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G18" s="31"/>
       <c r="H18" s="34"/>
@@ -10112,13 +10141,13 @@
         <v>1.0</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G19" s="31"/>
       <c r="H19" s="34"/>
